--- a/MiniTemplate/Datas/scale.xlsx
+++ b/MiniTemplate/Datas/scale.xlsx
@@ -1,48 +1,126 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D36980F-D2AB-49EF-AEA1-F2D362226AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>scaleValue</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>在当前场景下参照 item 的缩放倍率</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>抽奖时的物品展示倍率</t>
+  </si>
+  <si>
+    <t>missionReward</t>
+  </si>
+  <si>
+    <t>作为任务奖励时的倍率</t>
+  </si>
+  <si>
+    <t>missionIcon</t>
+  </si>
+  <si>
+    <t>作为任务图标时的倍率</t>
+  </si>
+  <si>
+    <t>convenience</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作为便利店商品时的倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -58,91 +136,32 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,222 +422,176 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="7.125" customWidth="1" style="2" min="2" max="2"/>
-    <col width="13.5" customWidth="1" style="2" min="3" max="3"/>
-    <col width="51.875" customWidth="1" style="2" min="4" max="4"/>
-    <col width="64.125" customWidth="1" style="2" min="5" max="5"/>
-    <col width="19" customWidth="1" style="2" min="6" max="6"/>
-    <col width="21.5" customWidth="1" style="2" min="7" max="8"/>
-    <col width="26.875" customWidth="1" style="2" min="9" max="9"/>
+    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="51.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="64.109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19" style="2" customWidth="1"/>
+    <col min="7" max="8" width="21.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.88671875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>scaleValue</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-      <c r="I3" s="1" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>在当前场景下参照 item 的缩放倍率</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-      <c r="I4" s="1" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="0" t="n">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>抽奖时的物品展示倍率</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="0" t="n">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>missionReward</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>作为任务奖励时的倍率</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1">
         <v>6000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="0" t="n">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>missionIcon</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>作为任务图标时的倍率</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1">
         <v>20000</v>
       </c>
     </row>
-    <row r="8">
-      <c r="C8" s="1" t="n"/>
-      <c r="D8" s="1" t="n"/>
-      <c r="E8" s="1" t="n"/>
-    </row>
-    <row r="9">
-      <c r="C9" s="1" t="n"/>
-      <c r="D9" s="1" t="n"/>
-      <c r="E9" s="1" t="n"/>
-    </row>
-    <row r="10">
-      <c r="C10" s="1" t="n"/>
-      <c r="D10" s="1" t="n"/>
-      <c r="E10" s="1" t="n"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="1" t="n"/>
-      <c r="D11" s="1" t="n"/>
-      <c r="E11" s="1" t="n"/>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MiniTemplate/Datas/scale.xlsx
+++ b/MiniTemplate/Datas/scale.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D36980F-D2AB-49EF-AEA1-F2D362226AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6010BCEC-31F4-495C-8885-CE381A3A6321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -87,6 +87,14 @@
   </si>
   <si>
     <t>作为便利店商品时的倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作为Buff时的倍率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -424,18 +432,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="64.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="51.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="64.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="19" style="2" customWidth="1"/>
-    <col min="7" max="8" width="21.44140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.88671875" style="2" customWidth="1"/>
+    <col min="7" max="8" width="21.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -456,7 +464,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -477,7 +485,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -498,7 +506,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -519,7 +527,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -533,7 +541,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2</v>
       </c>
@@ -547,7 +555,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3</v>
       </c>
@@ -561,7 +569,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -575,17 +583,26 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>

--- a/MiniTemplate/Datas/scale.xlsx
+++ b/MiniTemplate/Datas/scale.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6010BCEC-31F4-495C-8885-CE381A3A6321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C9DD05-BBB8-4535-AB80-9D8EBE0E5DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="744" windowWidth="30696" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -95,6 +95,14 @@
   </si>
   <si>
     <t>作为Buff时的倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>work</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在零工面板时的倍率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -432,18 +440,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="51.875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="64.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="51.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="64.109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="19" style="2" customWidth="1"/>
-    <col min="7" max="8" width="21.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.875" style="2" customWidth="1"/>
+    <col min="7" max="8" width="21.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.88671875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -464,7 +472,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -485,7 +493,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -506,7 +514,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -527,7 +535,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -541,7 +549,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
@@ -555,7 +563,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
@@ -569,7 +577,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -583,7 +591,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -597,12 +605,21 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>

--- a/MiniTemplate/Datas/scale.xlsx
+++ b/MiniTemplate/Datas/scale.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C9DD05-BBB8-4535-AB80-9D8EBE0E5DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E322E34C-720D-4D7F-9DFC-9F8F08210747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="744" windowWidth="30696" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -103,6 +103,14 @@
   </si>
   <si>
     <t>在零工面板时的倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mysIcon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在神秘转盘时的倍率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -440,18 +448,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="64.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="51.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="64.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="19" style="2" customWidth="1"/>
-    <col min="7" max="8" width="21.44140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.88671875" style="2" customWidth="1"/>
+    <col min="7" max="8" width="21.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -472,7 +480,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -493,7 +501,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -514,7 +522,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -535,7 +543,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -549,7 +557,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2</v>
       </c>
@@ -563,7 +571,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3</v>
       </c>
@@ -577,7 +585,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -591,7 +599,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -605,7 +613,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -619,10 +627,19 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B11" s="2">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="1">
+        <v>7000</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/MiniTemplate/Datas/scale.xlsx
+++ b/MiniTemplate/Datas/scale.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E322E34C-720D-4D7F-9DFC-9F8F08210747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0EE860-D9FC-4C6D-A845-BBCEE5CAEFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -111,6 +111,14 @@
   </si>
   <si>
     <t>在神秘转盘时的倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>communityCentre</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在社区中心冗余道具时的倍率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -164,7 +172,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -172,6 +180,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -447,19 +458,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="51.875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="64.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="51.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="64.109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="19" style="2" customWidth="1"/>
-    <col min="7" max="8" width="21.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.875" style="2" customWidth="1"/>
+    <col min="7" max="8" width="21.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.88671875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +491,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -501,7 +512,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -522,7 +533,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -543,7 +554,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -557,7 +568,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
@@ -571,7 +582,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
@@ -585,7 +596,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -599,7 +610,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -613,7 +624,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -627,7 +638,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -639,6 +650,20 @@
       </c>
       <c r="E11" s="1">
         <v>7000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="2">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="3">
+        <v>7500</v>
       </c>
     </row>
   </sheetData>
